--- a/docs/Decodifiche/151_dmnm_dec_tipo_professione.xlsx
+++ b/docs/Decodifiche/151_dmnm_dec_tipo_professione.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>ID</t>
   </si>
@@ -35,7 +35,7 @@
     <t>OCCUPATO/A</t>
   </si>
   <si>
-    <t>2025-12-02 20:23:14.0</t>
+    <t>2025-12-04 11:48:12.0</t>
   </si>
   <si>
     <t>9999-12-31 00:00:00.0</t>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>STUDENTE</t>
-  </si>
-  <si>
-    <t>2025-12-02 20:23:15.0</t>
   </si>
   <si>
     <t>7</t>
@@ -265,7 +262,7 @@
         <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -276,36 +273,36 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>21</v>
-      </c>
       <c r="C8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
